--- a/data/Raw_mat_basin.xlsx
+++ b/data/Raw_mat_basin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Quina_valleys\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F09E2BA-84F8-4C59-B770-719BD9862FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7031C9-03F9-4E8C-B017-4C4A7C4A82A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -99,11 +99,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Heqing basin</t>
+    <t>Caifeng</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Caifeng</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>Huangping basin</t>
   </si>
 </sst>
 </file>
@@ -485,21 +485,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J470"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="7" style="1" customWidth="1"/>
-    <col min="5" max="5" width="7.77734375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="7.6640625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="7.88671875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7.75" style="4" customWidth="1"/>
+    <col min="6" max="6" width="7.625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="7.875" style="4" customWidth="1"/>
     <col min="8" max="9" width="9" style="1"/>
-    <col min="10" max="10" width="10.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.625" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -531,7 +531,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -563,7 +563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -627,7 +627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -659,7 +659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -691,7 +691,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -723,7 +723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -755,7 +755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -787,7 +787,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -819,7 +819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -851,7 +851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -883,7 +883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -915,7 +915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -947,7 +947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>1</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>1</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>1</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>1</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>1</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>1</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>1</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>1</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>1</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>1</v>
       </c>
@@ -1491,7 +1491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>1</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>1</v>
       </c>
@@ -1587,7 +1587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>1</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>1</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>1</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>1</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>1</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>1</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>1</v>
       </c>
@@ -1811,7 +1811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>1</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>1</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>1</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>1</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>1</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>1</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>1</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>1</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>1</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>1</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>1</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>1</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>1</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>1</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>1</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>1</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>1</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>1</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>1</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>1</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>1</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>1</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>1</v>
       </c>
@@ -2547,7 +2547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>1</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>1</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>1</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>1</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>1</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>1</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>1</v>
       </c>
@@ -2771,7 +2771,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>1</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>1</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>1</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>1</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>1</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>1</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>1</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>1</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>1</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>1</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>1</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>1</v>
       </c>
@@ -3155,7 +3155,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>1</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>1</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>1</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>1</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>1</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>1</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>1</v>
       </c>
@@ -3379,7 +3379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>1</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>1</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>1</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>1</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>1</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>1</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>1</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>1</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>1</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>1</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>1</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>1</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>2</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>2</v>
       </c>
@@ -3827,7 +3827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>2</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>2</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>2</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>2</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>2</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>2</v>
       </c>
@@ -4019,7 +4019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>2</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>2</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>2</v>
       </c>
@@ -4115,7 +4115,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>2</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>2</v>
       </c>
@@ -4179,7 +4179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>2</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>2</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>2</v>
       </c>
@@ -4275,7 +4275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>2</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>2</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>2</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>2</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>2</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>2</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>2</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>2</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>2</v>
       </c>
@@ -4563,7 +4563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>2</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>2</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>2</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>2</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>2</v>
       </c>
@@ -4723,7 +4723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>2</v>
       </c>
@@ -4755,7 +4755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>2</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>2</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>2</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>2</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>2</v>
       </c>
@@ -4915,7 +4915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>2</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>2</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>2</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>2</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>2</v>
       </c>
@@ -5075,7 +5075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>2</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>2</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>2</v>
       </c>
@@ -5171,7 +5171,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>2</v>
       </c>
@@ -5203,7 +5203,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>2</v>
       </c>
@@ -5235,7 +5235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>2</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>2</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>2</v>
       </c>
@@ -5331,7 +5331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>2</v>
       </c>
@@ -5363,7 +5363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>2</v>
       </c>
@@ -5395,7 +5395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>2</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>2</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>2</v>
       </c>
@@ -5491,7 +5491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>2</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>2</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>2</v>
       </c>
@@ -5587,7 +5587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>2</v>
       </c>
@@ -5619,7 +5619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>2</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>2</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>2</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>2</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>2</v>
       </c>
@@ -5779,7 +5779,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>2</v>
       </c>
@@ -5811,7 +5811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>2</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>2</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>2</v>
       </c>
@@ -5907,7 +5907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>2</v>
       </c>
@@ -5939,7 +5939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>2</v>
       </c>
@@ -5971,7 +5971,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>2</v>
       </c>
@@ -6003,7 +6003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>2</v>
       </c>
@@ -6035,7 +6035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>2</v>
       </c>
@@ -6067,7 +6067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>2</v>
       </c>
@@ -6099,7 +6099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>2</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>2</v>
       </c>
@@ -6163,7 +6163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>2</v>
       </c>
@@ -6195,7 +6195,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>2</v>
       </c>
@@ -6227,7 +6227,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>2</v>
       </c>
@@ -6259,7 +6259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>2</v>
       </c>
@@ -6291,7 +6291,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>2</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>2</v>
       </c>
@@ -6355,7 +6355,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>2</v>
       </c>
@@ -6387,7 +6387,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>2</v>
       </c>
@@ -6419,7 +6419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>2</v>
       </c>
@@ -6451,7 +6451,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>2</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>2</v>
       </c>
@@ -6515,7 +6515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>2</v>
       </c>
@@ -6547,7 +6547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>2</v>
       </c>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>2</v>
       </c>
@@ -6611,7 +6611,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>2</v>
       </c>
@@ -6643,7 +6643,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>2</v>
       </c>
@@ -6675,7 +6675,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>2</v>
       </c>
@@ -6707,7 +6707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>2</v>
       </c>
@@ -6739,7 +6739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>2</v>
       </c>
@@ -6771,7 +6771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>2</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>2</v>
       </c>
@@ -6835,7 +6835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>2</v>
       </c>
@@ -6867,7 +6867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>2</v>
       </c>
@@ -6899,7 +6899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>2</v>
       </c>
@@ -6931,7 +6931,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>2</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>2</v>
       </c>
@@ -6995,7 +6995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>2</v>
       </c>
@@ -7027,7 +7027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>2</v>
       </c>
@@ -7059,7 +7059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>2</v>
       </c>
@@ -7091,7 +7091,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>2</v>
       </c>
@@ -7123,7 +7123,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>3</v>
       </c>
@@ -7155,7 +7155,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>3</v>
       </c>
@@ -7187,7 +7187,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>3</v>
       </c>
@@ -7219,7 +7219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>3</v>
       </c>
@@ -7251,7 +7251,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>3</v>
       </c>
@@ -7283,7 +7283,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>3</v>
       </c>
@@ -7315,7 +7315,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>3</v>
       </c>
@@ -7347,7 +7347,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>3</v>
       </c>
@@ -7379,7 +7379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>3</v>
       </c>
@@ -7411,7 +7411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>3</v>
       </c>
@@ -7443,7 +7443,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>3</v>
       </c>
@@ -7475,7 +7475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>3</v>
       </c>
@@ -7507,7 +7507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>3</v>
       </c>
@@ -7539,7 +7539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>3</v>
       </c>
@@ -7571,7 +7571,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>3</v>
       </c>
@@ -7603,7 +7603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>3</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>3</v>
       </c>
@@ -7667,7 +7667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>3</v>
       </c>
@@ -7699,7 +7699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>3</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>3</v>
       </c>
@@ -7763,7 +7763,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>3</v>
       </c>
@@ -7795,7 +7795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>3</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>3</v>
       </c>
@@ -7859,7 +7859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>3</v>
       </c>
@@ -7891,7 +7891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <v>3</v>
       </c>
@@ -7923,7 +7923,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <v>3</v>
       </c>
@@ -7955,7 +7955,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <v>3</v>
       </c>
@@ -7987,7 +7987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <v>3</v>
       </c>
@@ -8019,7 +8019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <v>3</v>
       </c>
@@ -8051,7 +8051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <v>3</v>
       </c>
@@ -8083,7 +8083,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <v>3</v>
       </c>
@@ -8115,7 +8115,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <v>3</v>
       </c>
@@ -8147,7 +8147,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <v>3</v>
       </c>
@@ -8179,7 +8179,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <v>3</v>
       </c>
@@ -8211,7 +8211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <v>3</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <v>3</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <v>3</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <v>3</v>
       </c>
@@ -8339,7 +8339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <v>3</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <v>3</v>
       </c>
@@ -8403,7 +8403,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <v>3</v>
       </c>
@@ -8435,7 +8435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <v>3</v>
       </c>
@@ -8467,7 +8467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <v>3</v>
       </c>
@@ -8499,7 +8499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <v>3</v>
       </c>
@@ -8531,7 +8531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <v>3</v>
       </c>
@@ -8563,7 +8563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <v>3</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <v>3</v>
       </c>
@@ -8627,7 +8627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <v>3</v>
       </c>
@@ -8659,7 +8659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <v>3</v>
       </c>
@@ -8691,7 +8691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <v>3</v>
       </c>
@@ -8723,7 +8723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <v>3</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <v>3</v>
       </c>
@@ -8787,7 +8787,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <v>3</v>
       </c>
@@ -8819,7 +8819,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <v>3</v>
       </c>
@@ -8851,7 +8851,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <v>3</v>
       </c>
@@ -8883,7 +8883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <v>3</v>
       </c>
@@ -8915,7 +8915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <v>3</v>
       </c>
@@ -8947,7 +8947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <v>3</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <v>3</v>
       </c>
@@ -9011,7 +9011,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <v>3</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <v>3</v>
       </c>
@@ -9075,7 +9075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <v>3</v>
       </c>
@@ -9107,7 +9107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <v>3</v>
       </c>
@@ -9139,7 +9139,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <v>3</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <v>3</v>
       </c>
@@ -9203,7 +9203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <v>3</v>
       </c>
@@ -9235,7 +9235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <v>3</v>
       </c>
@@ -9267,7 +9267,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <v>3</v>
       </c>
@@ -9299,7 +9299,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <v>3</v>
       </c>
@@ -9331,7 +9331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <v>3</v>
       </c>
@@ -9363,7 +9363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <v>3</v>
       </c>
@@ -9395,7 +9395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <v>3</v>
       </c>
@@ -9427,7 +9427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <v>3</v>
       </c>
@@ -9459,7 +9459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <v>3</v>
       </c>
@@ -9491,7 +9491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <v>3</v>
       </c>
@@ -9523,7 +9523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <v>3</v>
       </c>
@@ -9555,7 +9555,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <v>3</v>
       </c>
@@ -9587,7 +9587,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <v>3</v>
       </c>
@@ -9619,7 +9619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <v>3</v>
       </c>
@@ -9651,7 +9651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <v>3</v>
       </c>
@@ -9683,7 +9683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <v>3</v>
       </c>
@@ -9715,7 +9715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <v>3</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <v>3</v>
       </c>
@@ -9779,15 +9779,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <v>4</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D291" s="1">
         <v>9</v>
@@ -9811,15 +9811,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <v>4</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D292" s="1">
         <v>11</v>
@@ -9843,15 +9843,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <v>4</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D293" s="1">
         <v>16</v>
@@ -9875,15 +9875,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A294" s="1">
         <v>4</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D294" s="1">
         <v>17</v>
@@ -9907,15 +9907,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A295" s="1">
         <v>4</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D295" s="1">
         <v>20</v>
@@ -9939,15 +9939,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A296" s="1">
         <v>4</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D296" s="1">
         <v>21</v>
@@ -9971,15 +9971,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A297" s="1">
         <v>4</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D297" s="1">
         <v>29</v>
@@ -10003,15 +10003,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A298" s="1">
         <v>4</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D298" s="1">
         <v>31</v>
@@ -10035,15 +10035,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A299" s="1">
         <v>4</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D299" s="1">
         <v>32</v>
@@ -10067,15 +10067,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A300" s="1">
         <v>4</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D300" s="1">
         <v>35</v>
@@ -10099,15 +10099,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A301" s="1">
         <v>4</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D301" s="1">
         <v>45</v>
@@ -10131,15 +10131,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A302" s="1">
         <v>4</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D302" s="1">
         <v>47</v>
@@ -10163,15 +10163,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A303" s="1">
         <v>4</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D303" s="1">
         <v>53</v>
@@ -10195,15 +10195,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A304" s="1">
         <v>4</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D304" s="1">
         <v>54</v>
@@ -10227,15 +10227,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A305" s="1">
         <v>4</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D305" s="1">
         <v>57</v>
@@ -10259,15 +10259,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A306" s="1">
         <v>4</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D306" s="1">
         <v>67</v>
@@ -10291,15 +10291,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A307" s="1">
         <v>4</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D307" s="1">
         <v>90</v>
@@ -10323,15 +10323,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A308" s="1">
         <v>4</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D308" s="1">
         <v>64</v>
@@ -10355,15 +10355,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A309" s="1">
         <v>4</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D309" s="1">
         <v>56</v>
@@ -10387,15 +10387,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A310" s="1">
         <v>4</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D310" s="1">
         <v>51</v>
@@ -10419,15 +10419,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A311" s="1">
         <v>4</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D311" s="1">
         <v>52</v>
@@ -10451,15 +10451,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A312" s="1">
         <v>4</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D312" s="1">
         <v>55</v>
@@ -10483,15 +10483,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A313" s="1">
         <v>4</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D313" s="1">
         <v>73</v>
@@ -10515,15 +10515,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A314" s="1">
         <v>4</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D314" s="1">
         <v>75</v>
@@ -10547,15 +10547,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A315" s="1">
         <v>4</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D315" s="1">
         <v>81</v>
@@ -10579,15 +10579,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A316" s="1">
         <v>4</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D316" s="1">
         <v>87</v>
@@ -10611,15 +10611,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A317" s="1">
         <v>4</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D317" s="1">
         <v>1</v>
@@ -10643,15 +10643,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A318" s="1">
         <v>4</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D318" s="1">
         <v>2</v>
@@ -10675,15 +10675,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A319" s="1">
         <v>4</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D319" s="1">
         <v>3</v>
@@ -10707,15 +10707,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A320" s="1">
         <v>4</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D320" s="1">
         <v>4</v>
@@ -10739,15 +10739,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A321" s="1">
         <v>4</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D321" s="1">
         <v>5</v>
@@ -10771,15 +10771,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A322" s="1">
         <v>4</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D322" s="1">
         <v>6</v>
@@ -10803,15 +10803,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A323" s="1">
         <v>4</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D323" s="1">
         <v>7</v>
@@ -10835,15 +10835,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A324" s="1">
         <v>4</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D324" s="1">
         <v>8</v>
@@ -10867,15 +10867,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A325" s="1">
         <v>4</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D325" s="1">
         <v>10</v>
@@ -10899,15 +10899,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A326" s="1">
         <v>4</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D326" s="1">
         <v>12</v>
@@ -10931,15 +10931,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A327" s="1">
         <v>4</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D327" s="1">
         <v>13</v>
@@ -10963,15 +10963,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A328" s="1">
         <v>4</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D328" s="1">
         <v>14</v>
@@ -10995,15 +10995,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A329" s="1">
         <v>4</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D329" s="1">
         <v>15</v>
@@ -11027,15 +11027,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A330" s="1">
         <v>4</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D330" s="1">
         <v>18</v>
@@ -11059,15 +11059,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A331" s="1">
         <v>4</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D331" s="1">
         <v>19</v>
@@ -11091,15 +11091,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A332" s="1">
         <v>4</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D332" s="1">
         <v>22</v>
@@ -11123,15 +11123,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A333" s="1">
         <v>4</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D333" s="1">
         <v>23</v>
@@ -11155,15 +11155,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A334" s="1">
         <v>4</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D334" s="1">
         <v>24</v>
@@ -11187,15 +11187,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A335" s="1">
         <v>4</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D335" s="1">
         <v>25</v>
@@ -11219,15 +11219,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A336" s="1">
         <v>4</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D336" s="1">
         <v>26</v>
@@ -11251,15 +11251,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A337" s="1">
         <v>4</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D337" s="1">
         <v>27</v>
@@ -11283,15 +11283,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A338" s="1">
         <v>4</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D338" s="1">
         <v>28</v>
@@ -11315,15 +11315,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A339" s="1">
         <v>4</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D339" s="1">
         <v>30</v>
@@ -11347,15 +11347,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A340" s="1">
         <v>4</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D340" s="1">
         <v>33</v>
@@ -11379,15 +11379,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A341" s="1">
         <v>4</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D341" s="1">
         <v>34</v>
@@ -11411,15 +11411,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A342" s="1">
         <v>4</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D342" s="1">
         <v>36</v>
@@ -11443,15 +11443,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A343" s="1">
         <v>4</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D343" s="1">
         <v>37</v>
@@ -11475,15 +11475,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A344" s="1">
         <v>4</v>
       </c>
       <c r="B344" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D344" s="1">
         <v>38</v>
@@ -11507,15 +11507,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A345" s="1">
         <v>4</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D345" s="1">
         <v>39</v>
@@ -11539,15 +11539,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A346" s="1">
         <v>4</v>
       </c>
       <c r="B346" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D346" s="1">
         <v>40</v>
@@ -11571,15 +11571,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A347" s="1">
         <v>4</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D347" s="1">
         <v>41</v>
@@ -11603,15 +11603,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A348" s="1">
         <v>4</v>
       </c>
       <c r="B348" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C348" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D348" s="1">
         <v>42</v>
@@ -11635,15 +11635,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A349" s="1">
         <v>4</v>
       </c>
       <c r="B349" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D349" s="1">
         <v>43</v>
@@ -11667,15 +11667,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A350" s="1">
         <v>4</v>
       </c>
       <c r="B350" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C350" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D350" s="1">
         <v>44</v>
@@ -11699,15 +11699,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A351" s="1">
         <v>4</v>
       </c>
       <c r="B351" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D351" s="1">
         <v>46</v>
@@ -11731,15 +11731,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A352" s="1">
         <v>4</v>
       </c>
       <c r="B352" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C352" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D352" s="1">
         <v>48</v>
@@ -11763,15 +11763,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A353" s="1">
         <v>4</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D353" s="1">
         <v>49</v>
@@ -11795,15 +11795,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A354" s="1">
         <v>4</v>
       </c>
       <c r="B354" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D354" s="1">
         <v>50</v>
@@ -11827,15 +11827,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A355" s="1">
         <v>4</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D355" s="1">
         <v>58</v>
@@ -11859,15 +11859,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A356" s="1">
         <v>4</v>
       </c>
       <c r="B356" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C356" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D356" s="1">
         <v>59</v>
@@ -11891,15 +11891,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A357" s="1">
         <v>4</v>
       </c>
       <c r="B357" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D357" s="1">
         <v>60</v>
@@ -11923,15 +11923,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A358" s="1">
         <v>4</v>
       </c>
       <c r="B358" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C358" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D358" s="1">
         <v>61</v>
@@ -11955,15 +11955,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A359" s="1">
         <v>4</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D359" s="1">
         <v>62</v>
@@ -11987,15 +11987,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A360" s="1">
         <v>4</v>
       </c>
       <c r="B360" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C360" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D360" s="1">
         <v>63</v>
@@ -12019,15 +12019,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A361" s="1">
         <v>4</v>
       </c>
       <c r="B361" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D361" s="1">
         <v>65</v>
@@ -12051,15 +12051,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A362" s="1">
         <v>4</v>
       </c>
       <c r="B362" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C362" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D362" s="1">
         <v>66</v>
@@ -12083,15 +12083,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A363" s="1">
         <v>4</v>
       </c>
       <c r="B363" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D363" s="1">
         <v>68</v>
@@ -12115,15 +12115,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A364" s="1">
         <v>4</v>
       </c>
       <c r="B364" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C364" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D364" s="1">
         <v>69</v>
@@ -12147,15 +12147,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A365" s="1">
         <v>4</v>
       </c>
       <c r="B365" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D365" s="1">
         <v>70</v>
@@ -12179,15 +12179,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A366" s="1">
         <v>4</v>
       </c>
       <c r="B366" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C366" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D366" s="1">
         <v>71</v>
@@ -12211,15 +12211,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A367" s="1">
         <v>4</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D367" s="1">
         <v>72</v>
@@ -12243,15 +12243,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A368" s="1">
         <v>4</v>
       </c>
       <c r="B368" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C368" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D368" s="1">
         <v>74</v>
@@ -12275,15 +12275,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A369" s="1">
         <v>4</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D369" s="1">
         <v>76</v>
@@ -12307,15 +12307,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A370" s="1">
         <v>4</v>
       </c>
       <c r="B370" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C370" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D370" s="1">
         <v>77</v>
@@ -12339,15 +12339,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A371" s="1">
         <v>4</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D371" s="1">
         <v>78</v>
@@ -12371,15 +12371,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A372" s="1">
         <v>4</v>
       </c>
       <c r="B372" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C372" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D372" s="1">
         <v>79</v>
@@ -12403,15 +12403,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A373" s="1">
         <v>4</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D373" s="1">
         <v>80</v>
@@ -12435,15 +12435,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A374" s="1">
         <v>4</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C374" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D374" s="1">
         <v>82</v>
@@ -12467,15 +12467,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A375" s="1">
         <v>4</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D375" s="1">
         <v>83</v>
@@ -12499,15 +12499,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A376" s="1">
         <v>4</v>
       </c>
       <c r="B376" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C376" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D376" s="1">
         <v>84</v>
@@ -12531,15 +12531,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A377" s="1">
         <v>4</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D377" s="1">
         <v>85</v>
@@ -12563,15 +12563,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A378" s="1">
         <v>4</v>
       </c>
       <c r="B378" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C378" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D378" s="1">
         <v>86</v>
@@ -12595,15 +12595,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A379" s="1">
         <v>4</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D379" s="1">
         <v>88</v>
@@ -12627,15 +12627,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A380" s="1">
         <v>4</v>
       </c>
       <c r="B380" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C380" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D380" s="1">
         <v>89</v>
@@ -12659,15 +12659,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A381" s="1">
         <v>4</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D381" s="1">
         <v>91</v>
@@ -12691,15 +12691,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A382" s="1">
         <v>4</v>
       </c>
       <c r="B382" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C382" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D382" s="1">
         <v>92</v>
@@ -12723,15 +12723,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A383" s="1">
         <v>4</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D383" s="1">
         <v>93</v>
@@ -12755,15 +12755,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A384" s="1">
         <v>4</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C384" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D384" s="1">
         <v>94</v>
@@ -12787,15 +12787,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A385" s="1">
         <v>4</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D385" s="1">
         <v>95</v>
@@ -12819,15 +12819,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A386" s="1">
         <v>5</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C386" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D386" s="1">
         <v>3</v>
@@ -12851,15 +12851,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A387" s="1">
         <v>5</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D387" s="1">
         <v>35</v>
@@ -12883,15 +12883,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A388" s="1">
         <v>5</v>
       </c>
       <c r="B388" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D388" s="1">
         <v>37</v>
@@ -12915,15 +12915,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A389" s="1">
         <v>5</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D389" s="1">
         <v>38</v>
@@ -12947,15 +12947,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A390" s="1">
         <v>5</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C390" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D390" s="1">
         <v>44</v>
@@ -12979,15 +12979,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A391" s="1">
         <v>5</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D391" s="1">
         <v>51</v>
@@ -13011,15 +13011,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A392" s="1">
         <v>5</v>
       </c>
       <c r="B392" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C392" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D392" s="1">
         <v>54</v>
@@ -13043,15 +13043,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A393" s="1">
         <v>5</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D393" s="1">
         <v>57</v>
@@ -13075,15 +13075,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A394" s="1">
         <v>5</v>
       </c>
       <c r="B394" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C394" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D394" s="1">
         <v>66</v>
@@ -13107,15 +13107,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A395" s="1">
         <v>5</v>
       </c>
       <c r="B395" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D395" s="1">
         <v>70</v>
@@ -13139,15 +13139,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A396" s="1">
         <v>5</v>
       </c>
       <c r="B396" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C396" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D396" s="1">
         <v>72</v>
@@ -13156,7 +13156,7 @@
         <v>195</v>
       </c>
       <c r="F396" s="4">
-        <v>908</v>
+        <v>90.8</v>
       </c>
       <c r="G396" s="4">
         <v>58</v>
@@ -13171,15 +13171,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A397" s="1">
         <v>5</v>
       </c>
       <c r="B397" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D397" s="1">
         <v>75</v>
@@ -13203,15 +13203,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A398" s="1">
         <v>5</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C398" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D398" s="1">
         <v>77</v>
@@ -13235,15 +13235,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A399" s="1">
         <v>5</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D399" s="1">
         <v>79</v>
@@ -13267,15 +13267,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A400" s="1">
         <v>5</v>
       </c>
       <c r="B400" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C400" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D400" s="1">
         <v>82</v>
@@ -13299,15 +13299,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A401" s="1">
         <v>5</v>
       </c>
       <c r="B401" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D401" s="1">
         <v>4</v>
@@ -13331,15 +13331,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A402" s="1">
         <v>5</v>
       </c>
       <c r="B402" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C402" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D402" s="1">
         <v>10</v>
@@ -13363,15 +13363,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A403" s="1">
         <v>5</v>
       </c>
       <c r="B403" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D403" s="1">
         <v>22</v>
@@ -13395,15 +13395,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A404" s="1">
         <v>5</v>
       </c>
       <c r="B404" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C404" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D404" s="1">
         <v>32</v>
@@ -13427,15 +13427,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A405" s="1">
         <v>5</v>
       </c>
       <c r="B405" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D405" s="1">
         <v>34</v>
@@ -13459,15 +13459,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A406" s="1">
         <v>5</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C406" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D406" s="1">
         <v>39</v>
@@ -13491,15 +13491,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A407" s="1">
         <v>5</v>
       </c>
       <c r="B407" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D407" s="1">
         <v>45</v>
@@ -13523,15 +13523,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A408" s="1">
         <v>5</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C408" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D408" s="1">
         <v>46</v>
@@ -13555,15 +13555,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A409" s="1">
         <v>5</v>
       </c>
       <c r="B409" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D409" s="1">
         <v>61</v>
@@ -13587,15 +13587,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A410" s="1">
         <v>5</v>
       </c>
       <c r="B410" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C410" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D410" s="1">
         <v>62</v>
@@ -13619,15 +13619,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A411" s="1">
         <v>5</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D411" s="1">
         <v>21</v>
@@ -13651,15 +13651,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A412" s="1">
         <v>5</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C412" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D412" s="1">
         <v>1</v>
@@ -13683,15 +13683,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A413" s="1">
         <v>5</v>
       </c>
       <c r="B413" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D413" s="1">
         <v>2</v>
@@ -13715,15 +13715,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A414" s="1">
         <v>5</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C414" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D414" s="1">
         <v>5</v>
@@ -13747,15 +13747,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A415" s="1">
         <v>5</v>
       </c>
       <c r="B415" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D415" s="1">
         <v>6</v>
@@ -13779,15 +13779,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A416" s="1">
         <v>5</v>
       </c>
       <c r="B416" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C416" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D416" s="1">
         <v>7</v>
@@ -13811,15 +13811,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A417" s="1">
         <v>5</v>
       </c>
       <c r="B417" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D417" s="1">
         <v>8</v>
@@ -13843,15 +13843,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A418" s="1">
         <v>5</v>
       </c>
       <c r="B418" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C418" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D418" s="1">
         <v>9</v>
@@ -13875,15 +13875,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A419" s="1">
         <v>5</v>
       </c>
       <c r="B419" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D419" s="1">
         <v>11</v>
@@ -13907,15 +13907,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A420" s="1">
         <v>5</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D420" s="1">
         <v>12</v>
@@ -13939,15 +13939,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A421" s="1">
         <v>5</v>
       </c>
       <c r="B421" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D421" s="1">
         <v>13</v>
@@ -13971,15 +13971,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A422" s="1">
         <v>5</v>
       </c>
       <c r="B422" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C422" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D422" s="1">
         <v>14</v>
@@ -14003,15 +14003,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A423" s="1">
         <v>5</v>
       </c>
       <c r="B423" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D423" s="1">
         <v>15</v>
@@ -14035,15 +14035,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A424" s="1">
         <v>5</v>
       </c>
       <c r="B424" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C424" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D424" s="1">
         <v>16</v>
@@ -14067,15 +14067,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A425" s="1">
         <v>5</v>
       </c>
       <c r="B425" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D425" s="1">
         <v>17</v>
@@ -14099,15 +14099,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A426" s="1">
         <v>5</v>
       </c>
       <c r="B426" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C426" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D426" s="1">
         <v>18</v>
@@ -14131,15 +14131,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A427" s="1">
         <v>5</v>
       </c>
       <c r="B427" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D427" s="1">
         <v>19</v>
@@ -14163,15 +14163,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A428" s="1">
         <v>5</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C428" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D428" s="1">
         <v>20</v>
@@ -14195,15 +14195,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A429" s="1">
         <v>5</v>
       </c>
       <c r="B429" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D429" s="1">
         <v>23</v>
@@ -14227,15 +14227,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A430" s="1">
         <v>5</v>
       </c>
       <c r="B430" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C430" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D430" s="1">
         <v>24</v>
@@ -14259,15 +14259,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A431" s="1">
         <v>5</v>
       </c>
       <c r="B431" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D431" s="1">
         <v>25</v>
@@ -14291,15 +14291,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A432" s="1">
         <v>5</v>
       </c>
       <c r="B432" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C432" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D432" s="1">
         <v>26</v>
@@ -14323,15 +14323,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A433" s="1">
         <v>5</v>
       </c>
       <c r="B433" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D433" s="1">
         <v>27</v>
@@ -14355,15 +14355,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A434" s="1">
         <v>5</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C434" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D434" s="1">
         <v>28</v>
@@ -14387,15 +14387,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A435" s="1">
         <v>5</v>
       </c>
       <c r="B435" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D435" s="1">
         <v>29</v>
@@ -14419,15 +14419,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A436" s="1">
         <v>5</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C436" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D436" s="1">
         <v>30</v>
@@ -14451,15 +14451,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A437" s="1">
         <v>5</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D437" s="1">
         <v>31</v>
@@ -14483,15 +14483,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A438" s="1">
         <v>5</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C438" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D438" s="1">
         <v>33</v>
@@ -14515,15 +14515,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A439" s="1">
         <v>5</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D439" s="1">
         <v>36</v>
@@ -14547,15 +14547,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A440" s="1">
         <v>5</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C440" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D440" s="1">
         <v>40</v>
@@ -14579,15 +14579,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A441" s="1">
         <v>5</v>
       </c>
       <c r="B441" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D441" s="1">
         <v>41</v>
@@ -14611,15 +14611,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A442" s="1">
         <v>5</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C442" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D442" s="1">
         <v>42</v>
@@ -14643,15 +14643,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A443" s="1">
         <v>5</v>
       </c>
       <c r="B443" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D443" s="1">
         <v>43</v>
@@ -14675,15 +14675,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A444" s="1">
         <v>5</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C444" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D444" s="1">
         <v>47</v>
@@ -14707,15 +14707,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A445" s="1">
         <v>5</v>
       </c>
       <c r="B445" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D445" s="1">
         <v>48</v>
@@ -14739,15 +14739,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A446" s="1">
         <v>5</v>
       </c>
       <c r="B446" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C446" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D446" s="1">
         <v>49</v>
@@ -14771,15 +14771,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A447" s="1">
         <v>5</v>
       </c>
       <c r="B447" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D447" s="1">
         <v>50</v>
@@ -14803,15 +14803,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A448" s="1">
         <v>5</v>
       </c>
       <c r="B448" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C448" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D448" s="1">
         <v>52</v>
@@ -14835,15 +14835,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A449" s="1">
         <v>5</v>
       </c>
       <c r="B449" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D449" s="1">
         <v>53</v>
@@ -14867,15 +14867,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A450" s="1">
         <v>5</v>
       </c>
       <c r="B450" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C450" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D450" s="1">
         <v>55</v>
@@ -14899,15 +14899,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A451" s="1">
         <v>5</v>
       </c>
       <c r="B451" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D451" s="1">
         <v>56</v>
@@ -14931,15 +14931,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A452" s="1">
         <v>5</v>
       </c>
       <c r="B452" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C452" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D452" s="1">
         <v>58</v>
@@ -14963,15 +14963,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A453" s="1">
         <v>5</v>
       </c>
       <c r="B453" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D453" s="1">
         <v>59</v>
@@ -14995,15 +14995,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A454" s="1">
         <v>5</v>
       </c>
       <c r="B454" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C454" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D454" s="1">
         <v>60</v>
@@ -15027,15 +15027,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A455" s="1">
         <v>5</v>
       </c>
       <c r="B455" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D455" s="1">
         <v>63</v>
@@ -15059,15 +15059,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A456" s="1">
         <v>5</v>
       </c>
       <c r="B456" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C456" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D456" s="1">
         <v>64</v>
@@ -15091,15 +15091,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A457" s="1">
         <v>5</v>
       </c>
       <c r="B457" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D457" s="1">
         <v>65</v>
@@ -15123,15 +15123,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A458" s="1">
         <v>5</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C458" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D458" s="1">
         <v>67</v>
@@ -15155,15 +15155,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A459" s="1">
         <v>5</v>
       </c>
       <c r="B459" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D459" s="1">
         <v>68</v>
@@ -15187,15 +15187,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A460" s="1">
         <v>5</v>
       </c>
       <c r="B460" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C460" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D460" s="1">
         <v>69</v>
@@ -15219,15 +15219,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A461" s="1">
         <v>5</v>
       </c>
       <c r="B461" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D461" s="1">
         <v>71</v>
@@ -15251,15 +15251,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A462" s="1">
         <v>5</v>
       </c>
       <c r="B462" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C462" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D462" s="1">
         <v>73</v>
@@ -15283,15 +15283,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A463" s="1">
         <v>5</v>
       </c>
       <c r="B463" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D463" s="1">
         <v>74</v>
@@ -15315,15 +15315,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A464" s="1">
         <v>5</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C464" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D464" s="1">
         <v>76</v>
@@ -15347,15 +15347,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A465" s="1">
         <v>5</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D465" s="1">
         <v>78</v>
@@ -15379,15 +15379,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A466" s="1">
         <v>5</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C466" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D466" s="1">
         <v>80</v>
@@ -15411,15 +15411,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A467" s="1">
         <v>5</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D467" s="1">
         <v>81</v>
@@ -15443,15 +15443,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A468" s="1">
         <v>5</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C468" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D468" s="1">
         <v>83</v>
@@ -15475,15 +15475,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A469" s="1">
         <v>5</v>
       </c>
       <c r="B469" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D469" s="1">
         <v>84</v>
@@ -15507,15 +15507,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A470" s="1">
         <v>5</v>
       </c>
       <c r="B470" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C470" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D470" s="1">
         <v>85</v>
